--- a/IMRADS/Map Visualizer/BNST_alloc.xlsx
+++ b/IMRADS/Map Visualizer/BNST_alloc.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PERSONAL\BRYAN\bulsu\Thesis 1\ShelterAlloc_Thesis\IMRADS\Map Visualizer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D1FC5A-9CBA-481C-BD26-447B67335CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF04F55-10E5-4C4B-A85B-11A88D900E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$30</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -548,13 +551,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.28515625" customWidth="1"/>
-    <col min="3" max="3" width="45.5703125" customWidth="1"/>
+    <col min="1" max="1" width="18.44140625" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" customWidth="1"/>
+    <col min="3" max="3" width="45.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -568,91 +572,91 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>36</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>36</v>
       </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
-      </c>
       <c r="D7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -660,141 +664,141 @@
         <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>11</v>
       </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D13">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D17">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
         <v>40</v>
@@ -806,9 +810,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B19" t="s">
         <v>35</v>
@@ -820,68 +824,68 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" t="s">
         <v>34</v>
-      </c>
-      <c r="D20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" t="s">
-        <v>32</v>
       </c>
       <c r="C24" t="s">
         <v>34</v>
@@ -890,68 +894,68 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D25">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D26">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" t="s">
         <v>40</v>
       </c>
-      <c r="C27" t="s">
-        <v>35</v>
-      </c>
       <c r="D27">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D28">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s">
         <v>40</v>
@@ -960,21 +964,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D30">
         <v>2</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D30" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D30">
+      <sortCondition ref="B1:B30"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>